--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486779_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486779_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2662</v>
+        <v>5.6153</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4153</v>
+        <v>4.367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.851</v>
+        <v>1.2483</v>
       </c>
       <c r="G2" t="n">
         <v>3.585</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>0.044</v>
+        <v>0.3931</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0548</v>
+        <v>0.0066</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0108</v>
+        <v>0.3865</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1546</v>
+        <v>4.7228</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6583</v>
+        <v>5.1272</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5037</v>
+        <v>-0.4044</v>
       </c>
       <c r="G3" t="n">
         <v>3.3302</v>
@@ -688,13 +688,13 @@
         <v>2.8962</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3144</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3039</v>
+        <v>0.165</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6183</v>
+        <v>0.7176</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2277</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9901</v>
+        <v>4.1928</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9595</v>
+        <v>3.063</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0305</v>
+        <v>1.1298</v>
       </c>
       <c r="G4" t="n">
         <v>4.0704</v>
@@ -766,13 +766,13 @@
         <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4523</v>
+        <v>0.655</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1659</v>
+        <v>-0.0625</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6182</v>
+        <v>0.7175</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8842</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2404</v>
+        <v>2.4543</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3062</v>
+        <v>1.8925</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9342</v>
+        <v>0.5617</v>
       </c>
       <c r="G5" t="n">
         <v>1.3181</v>
@@ -844,13 +844,13 @@
         <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8757</v>
+        <v>1.0895</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7443</v>
+        <v>0.3306</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1314</v>
+        <v>0.7589</v>
       </c>
       <c r="V5" t="n">
         <v>-1.8842</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>J. CEBRIAN SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3215</v>
+        <v>0.1516</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9363</v>
+        <v>-0.0552</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6148</v>
+        <v>0.2068</v>
       </c>
       <c r="G6" t="n">
-        <v>1.591</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6897</v>
+        <v>-0.2069</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0987</v>
+        <v>0.1379</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6746</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.242</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5674</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0837</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5524</v>
+        <v>-0.2069</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5313</v>
+        <v>0.1379</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1167</v>
+        <v>0.0276</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1233</v>
+        <v>-0.0552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9935</v>
+        <v>0.0828</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1816</v>
+        <v>0.1071</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9224</v>
+        <v>0.8479</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6168</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>0.833</v>
+        <v>0.7585</v>
       </c>
       <c r="T7" t="n">
         <v>0.4688</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3643</v>
+        <v>0.2898</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CEBRIAN SOLER</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.102</v>
+        <v>-0.8852</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0552</v>
+        <v>-0.9308</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1572</v>
+        <v>0.0456</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-1.0506</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2069</v>
+        <v>1.669</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1379</v>
+        <v>-2.7195</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.6402</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.0146</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.3744</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-1.6907</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2069</v>
+        <v>-0.3456</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1379</v>
+        <v>-1.3451</v>
       </c>
       <c r="P8" t="n">
         <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1931</v>
+        <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0221</v>
+        <v>0.5861</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0552</v>
+        <v>0.1168</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0331</v>
+        <v>0.4693</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6147</v>
+        <v>-1.5471</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7099</v>
+        <v>-0.5598</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09520000000000001</v>
+        <v>-0.9873</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0506</v>
+        <v>1.591</v>
       </c>
       <c r="H9" t="n">
-        <v>1.669</v>
+        <v>2.6897</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7195</v>
+        <v>-1.0987</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6402</v>
+        <v>2.6746</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0146</v>
+        <v>3.242</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3744</v>
+        <v>-0.5674</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6907</v>
+        <v>-1.0837</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3456</v>
+        <v>-0.5524</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3451</v>
+        <v>-0.5313</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1434</v>
+        <v>1.2481</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6623</v>
+        <v>0.6271</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5189</v>
+        <v>0.621</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6138</v>
+        <v>-2.4554</v>
       </c>
       <c r="W9" t="n">
-        <v>0.243</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8568</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0086</v>
+        <v>-1.9025</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3629</v>
+        <v>-3.4804</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3543</v>
+        <v>1.5778</v>
       </c>
       <c r="G10" t="n">
         <v>0.3952</v>
@@ -1234,13 +1234,13 @@
         <v>3.0892</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8165</v>
+        <v>0.2895</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1038</v>
+        <v>-0.2212</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2872</v>
+        <v>0.5107</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6565</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.6331</v>
+        <v>12.9091</v>
       </c>
       <c r="E11" t="n">
-        <v>8.406799999999999</v>
+        <v>8.682700000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2263</v>
+        <v>4.2262</v>
       </c>
       <c r="G11" t="n">
         <v>11.5535</v>
@@ -1312,10 +1312,10 @@
         <v>18.3425</v>
       </c>
       <c r="S11" t="n">
-        <v>5.6541</v>
+        <v>5.93</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1001</v>
+        <v>1.376</v>
       </c>
       <c r="U11" t="n">
         <v>4.5541</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3151</v>
+        <v>3.2421</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0447</v>
+        <v>3.7345</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7296</v>
+        <v>-0.4924</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6006</v>
@@ -1390,13 +1390,13 @@
         <v>1.7377</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3199</v>
+        <v>-0.393</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2486</v>
+        <v>-0.5589</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0713</v>
+        <v>0.1659</v>
       </c>
       <c r="V12" t="n">
         <v>2.498</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.514</v>
+        <v>1.7264</v>
       </c>
       <c r="E13" t="n">
         <v>0.8774</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.849</v>
       </c>
       <c r="G13" t="n">
         <v>1.2286</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9157</v>
+        <v>-0.7033</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4691</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4466</v>
+        <v>-0.2342</v>
       </c>
       <c r="V13" t="n">
         <v>0.0426</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0029</v>
+        <v>0.4549</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7128</v>
+        <v>3.9197</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7157</v>
+        <v>-3.4647</v>
       </c>
       <c r="G14" t="n">
         <v>0.9045</v>
@@ -1546,13 +1546,13 @@
         <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9266</v>
+        <v>-0.4688</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6347</v>
+        <v>-0.4278</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.292</v>
+        <v>-0.041</v>
       </c>
       <c r="V14" t="n">
         <v>0.9847</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0467</v>
+        <v>-0.5571</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4647</v>
+        <v>2.5681</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5115</v>
+        <v>-3.1252</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7883</v>
@@ -1624,13 +1624,13 @@
         <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6825</v>
+        <v>-1.1929</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8829</v>
+        <v>-0.7795</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7996</v>
+        <v>-0.4134</v>
       </c>
       <c r="V15" t="n">
         <v>3.3548</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4637</v>
+        <v>-1.1976</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5524</v>
+        <v>-2.449</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0887</v>
+        <v>1.2514</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2914</v>
@@ -1702,13 +1702,13 @@
         <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9213</v>
+        <v>-0.6552</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7175</v>
+        <v>-0.6141</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2038</v>
+        <v>-0.0411</v>
       </c>
       <c r="V16" t="n">
         <v>0.3282</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7299</v>
+        <v>-2.3381</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9685</v>
+        <v>-2.1753</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7614</v>
+        <v>-0.1628</v>
       </c>
       <c r="G17" t="n">
         <v>-2.2791</v>
@@ -1780,13 +1780,13 @@
         <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6125</v>
+        <v>-0.2208</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1936</v>
+        <v>-0.4004</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.419</v>
+        <v>0.1796</v>
       </c>
       <c r="V17" t="n">
         <v>1.5133</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7169</v>
+        <v>-3.4218</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.9103</v>
+        <v>-3.7035</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1935</v>
+        <v>0.2817</v>
       </c>
       <c r="G18" t="n">
         <v>-4.7763</v>
@@ -1858,13 +1858,13 @@
         <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8054</v>
+        <v>-0.5103</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8279</v>
+        <v>-0.621</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.1107</v>
       </c>
       <c r="V18" t="n">
         <v>0.8995</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1659</v>
+        <v>-4.2081</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.4075</v>
+        <v>-1.3839</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2416</v>
+        <v>-2.8242</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.405</v>
+        <v>-2.5459</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.738</v>
+        <v>-1.9242</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.667</v>
+        <v>-0.6217</v>
       </c>
       <c r="J19" t="n">
-        <v>0.024</v>
+        <v>-0.5039</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2202</v>
+        <v>-0.5446</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2442</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4289</v>
+        <v>-2.042</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5178</v>
+        <v>-1.3796</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9111</v>
+        <v>-0.6624</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.7031</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.827</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8996</v>
+        <v>-0.2413</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2763</v>
+        <v>-0.2001</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1759</v>
+        <v>-0.0412</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0426</v>
+        <v>-1.2277</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3282</v>
+        <v>0.2856</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3709</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3363</v>
+        <v>-4.9549</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4873</v>
+        <v>-5.6143</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.849</v>
+        <v>0.6594</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5459</v>
+        <v>-2.405</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9242</v>
+        <v>-1.738</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6217</v>
+        <v>-0.667</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5039</v>
+        <v>0.024</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5446</v>
+        <v>-0.2202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>0.2442</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.042</v>
+        <v>-2.4289</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3796</v>
+        <v>-1.5178</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6624</v>
+        <v>-0.9111</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1931</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-4.827</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3696</v>
+        <v>0.1105</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3036</v>
+        <v>-0.4831</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.066</v>
+        <v>0.5936</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2277</v>
+        <v>0.0426</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2856</v>
+        <v>-0.3282</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5133</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-12.6332</v>
+        <v>-11.2542</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.226400000000001</v>
+        <v>-4.2263</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.4068</v>
+        <v>-7.0278</v>
       </c>
       <c r="G21" t="n">
         <v>-11.5535</v>
@@ -2065,7 +2065,7 @@
         <v>-1.2098</v>
       </c>
       <c r="J21" t="n">
-        <v>8.077199999999999</v>
+        <v>8.077199999999998</v>
       </c>
       <c r="K21" t="n">
         <v>2.0748</v>
@@ -2092,13 +2092,13 @@
         <v>14.4809</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.6539</v>
+        <v>-4.2751</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.554200000000001</v>
+        <v>-4.554</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1</v>
+        <v>0.2789000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>8.436</v>
